--- a/diseases/d237/2026-2029.xlsx
+++ b/diseases/d237/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>1156</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>10.80268177509555</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>1054</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>9.849503971410646</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>1085</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>10.13919526468743</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>1141</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>10.6625085686713</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1053</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>9.840159090982363</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>1060</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>9.905573253980346</v>
       </c>
@@ -3136,16 +3118,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="O14" t="n">
-        <v>1106</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
+        <v>1105</v>
       </c>
       <c r="R14" t="n">
-        <v>10.33543775368138</v>
+        <v>10.3260928732531</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -3298,10 +3277,10 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="O15" t="n">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -3643,7 +3622,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7655</v>
+        <v>7654</v>
       </c>
     </row>
     <row r="16">
